--- a/files/g2-01-func-production.xlsx
+++ b/files/g2-01-func-production.xlsx
@@ -899,7 +899,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>생산일보   — 표의 노란 열 5개(J~N) + 아래쪽 집계 38문제</t>
+          <t>생산일보   — 표의 노란 열 5개(J~N) + 아래쪽 집계 39문제</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>■ 집계 문제 38개 — 번호 옆 ▶ 표시된 칸(F열)에 수식을 넣으세요</t>
+          <t>■ 집계 문제 39개 — 번호 옆 ▶ 표시된 칸(F열)에 수식을 넣으세요</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  집계 문제 38개</t>
+          <t xml:space="preserve">  집계 문제 39개</t>
         </is>
       </c>
     </row>
